--- a/output/full_scan/batch_seq0_2026-10-12.xlsx
+++ b/output/full_scan/batch_seq0_2026-10-12.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O114"/>
+  <dimension ref="A1:O115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>9105</v>
+        <v>8070</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1008.113483580041</v>
+        <v>1229.54371987767</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9.050000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>62.18653879787273</v>
+        <v>59.96390649259295</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>22.44921937425629</v>
+        <v>18.4898240317134</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.911348358004098</v>
+        <v>1.65494959381451</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.051833246891799</v>
+        <v>0.1730397877901714</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8070</v>
+        <v>9105</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>924.5437198776764</v>
+        <v>1188.113483580041</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>52.2</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>59.96390663555234</v>
+        <v>62.18653879787273</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>18.48982402419547</v>
+        <v>22.44921946072353</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.65494959381451</v>
+        <v>2.911348358004098</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1730397876339404</v>
+        <v>0.0518332468701684</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8089</v>
+        <v>8042</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>911.4005376748846</v>
+        <v>1083.404548999648</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>20.8</v>
+        <v>144</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>71.75315693848005</v>
+        <v>71.42592501222836</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>31.07253619321775</v>
+        <v>31.24567015730007</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4.240053767488464</v>
+        <v>4.440454899964779</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1087909324294195</v>
+        <v>3.164347669908731</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8042</v>
+        <v>8996</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>883.4045489996478</v>
+        <v>1068.594029986011</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>144</v>
+        <v>1720</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>71.42592506918527</v>
+        <v>67.61591985005717</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>31.2456701324599</v>
+        <v>40.56172697166608</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>4.440454899964779</v>
+        <v>0.1853386966204923</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>3.16434766915164</v>
+        <v>13.04079861144862</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8932</v>
+        <v>8089</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>825.6425533647523</v>
+        <v>1051.400537674885</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>97</v>
+        <v>20.8</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>56.25077065590714</v>
+        <v>71.75315687060234</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>17.23521319731513</v>
+        <v>31.0725364271477</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.85976036884572</v>
+        <v>4.240053767488464</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.7664223735673223</v>
+        <v>0.1087909321049499</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8431</v>
+        <v>8213</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>809.7788645038808</v>
+        <v>1023.41493803855</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>65.5</v>
+        <v>39.15</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>56.88114792906548</v>
+        <v>80.07022667501569</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>29.85309386927291</v>
+        <v>33.27066715099073</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.081186716120326</v>
+        <v>2.941493803855005</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.6322310996849816</v>
+        <v>0.6156714906845338</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8171</v>
+        <v>8932</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>785.7991792423788</v>
+        <v>965.6425533647524</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>22.35</v>
+        <v>97</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>79.30272235134838</v>
+        <v>56.25077123151524</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>23.95213638354145</v>
+        <v>17.23521325980293</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3.679917924237887</v>
+        <v>1.85976036884572</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.149959025227795</v>
+        <v>0.7664223702720463</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8093</v>
+        <v>8171</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>752.7648500707093</v>
+        <v>955.7991792423788</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>27.8</v>
+        <v>22.35</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>57.18259867898166</v>
+        <v>79.30272245347047</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>13.29987217121353</v>
+        <v>23.95213635764307</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3.917950731180685</v>
+        <v>3.679917924237887</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.3114810051268049</v>
+        <v>0.1499590250475365</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8068</v>
+        <v>8431</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>724</v>
+        <v>924.7788645038808</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>19.65</v>
+        <v>65.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>71.00630753939642</v>
+        <v>56.88114796039608</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>31.29789188036909</v>
+        <v>29.85309387529854</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>5.237894930505611</v>
+        <v>2.081186716120326</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2291877649889963</v>
+        <v>-0.6322310993725271</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8213</v>
+        <v>8093</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>713.4149380385501</v>
+        <v>922.7648500707091</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>39.15</v>
+        <v>27.8</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>80.07022674508553</v>
+        <v>57.18259869667595</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>33.27066712064481</v>
+        <v>13.29987218011323</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.941493803855005</v>
+        <v>3.917950731180685</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.6156714907205826</v>
+        <v>0.3114810050238265</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8150</v>
+        <v>8068</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>695.8400513292214</v>
+        <v>894</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>123</v>
+        <v>19.65</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>65.83443002220663</v>
+        <v>71.00630751793962</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>42.28277904356575</v>
+        <v>31.29789185292028</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.6472964658143184</v>
+        <v>5.237894930505611</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>2.026739351854003</v>
+        <v>0.229187764868826</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8114</v>
+        <v>8086</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>694.2730555421067</v>
+        <v>861.7941984440338</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>180.5</v>
+        <v>148.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>45.96614912011909</v>
+        <v>74.25423804172596</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>22.90060216854668</v>
+        <v>29.31409655904447</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.245329928606275</v>
+        <v>4.656524599440434</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,11 +1153,11 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.153281947844876</v>
+        <v>4.773342913011708</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, breakout_volume_confirm, cci_momentum</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>678.2598036800654</v>
+        <v>848.2598036800654</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>60</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>73.89009628322395</v>
+        <v>73.89009625615742</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>34.02808842946192</v>
+        <v>34.02808845543495</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>4.633327227037014</v>
@@ -1206,11 +1206,11 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1.670764654814223</v>
+        <v>1.670764654850278</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>674.2693615794968</v>
+        <v>814.2693615794969</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>48.65</v>
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>69.09322141305432</v>
+        <v>69.0932215087274</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>14.82499179349408</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.2880418395916416</v>
+        <v>0.2880418392791932</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8046</v>
+        <v>9103</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>668.3136900408572</v>
+        <v>805.8144416975947</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1440</v>
+        <v>6.46</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>65.63420094574974</v>
+        <v>87.35677322238962</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>29.5892118704852</v>
+        <v>23.98919094573951</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.6106243430834133</v>
+        <v>2.681444169759468</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>26.0162915191903</v>
+        <v>0.1432198992423591</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8086</v>
+        <v>8455</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>661.7941984440338</v>
+        <v>804</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>148.5</v>
+        <v>25.2</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>74.25423807349125</v>
+        <v>52.84115313778592</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>29.31409655068507</v>
+        <v>10.11572949116053</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>4.656524599440434</v>
+        <v>5.036644765792149</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>4.773342913612568</v>
+        <v>-0.1552145861991101</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8111</v>
+        <v>8150</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>657.3443960855127</v>
+        <v>800.8400513292214</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>84.40000000000001</v>
+        <v>123</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,49 +1400,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>56.49735439474414</v>
+        <v>65.83443003749198</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>39.46334217292591</v>
+        <v>42.28277920315605</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.8790520595010514</v>
+        <v>0.6472964658143184</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.7391356283499562</v>
+        <v>2.026739351673752</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8240</v>
+        <v>8046</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>648.8775930035323</v>
+        <v>788.3136900408572</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>54.5</v>
+        <v>1440</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>55.20473590534355</v>
+        <v>65.6342009252734</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>36.60985081605504</v>
+        <v>29.58921181967717</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.196662363998827</v>
+        <v>0.6106243430834133</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.2272161554909213</v>
+        <v>26.01629151846929</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8234</v>
+        <v>8069</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>640.9816683238179</v>
+        <v>774.4110370602718</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>64.40000000000001</v>
+        <v>149</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,29 +1506,29 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>53.50966885326877</v>
+        <v>49.27675654034378</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>17.27792666955223</v>
+        <v>25.47012012888024</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.282405907416796</v>
+        <v>1.540518203012892</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.3459216556132856</v>
+        <v>1.3229600826749</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, cci_momentum</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>634.0841222928771</v>
+        <v>769.0841222928768</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>41.7</v>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>63.77260656740022</v>
+        <v>63.77260662933647</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>14.8939871251811</v>
+        <v>14.89398715080442</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>2.197808385003554</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.0927146353387924</v>
+        <v>0.0927146353147606</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>9103</v>
+        <v>8234</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>605.8144416975947</v>
+        <v>755.9816683238181</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>6.46</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>87.35677319779849</v>
+        <v>53.50966889137408</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>23.98919093782077</v>
+        <v>17.27792668408021</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.681444169759468</v>
+        <v>2.282405907416796</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1432198992495697</v>
+        <v>0.3459216541712144</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8455</v>
+        <v>8464</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>604</v>
+        <v>723.9250070260335</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>25.2</v>
+        <v>372.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,49 +1665,49 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>52.84115313778592</v>
+        <v>53.55228823468913</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>10.11572950117861</v>
+        <v>10.40551863665555</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>5.036644765792149</v>
+        <v>1.408649710434518</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.1552145860188474</v>
+        <v>-0.107016665564096</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8215</v>
+        <v>8092</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>592.7527710957993</v>
+        <v>721.2632945696819</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>27.8</v>
+        <v>12.8</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>53.1757150708864</v>
+        <v>52.73050628928792</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>38.05655168468371</v>
+        <v>14.72347670489362</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.1942390485610783</v>
+        <v>4.226329456968185</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.11199647532426</v>
+        <v>0.0175774684086504</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8092</v>
+        <v>8081</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>581.2632945696819</v>
+        <v>713.9572737650454</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>12.8</v>
+        <v>262.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>52.73050644769484</v>
+        <v>60.17824365532431</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>14.72347672002504</v>
+        <v>15.06139683116637</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>4.226329456968185</v>
+        <v>0.9863980664826718</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0175774684206673</v>
+        <v>1.548283643966364</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8048</v>
+        <v>8467</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>578.374159426352</v>
+        <v>694.784370156995</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>52.5</v>
+        <v>92.3</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>61.26991336075693</v>
+        <v>55.6399104077677</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>13.2167054832131</v>
+        <v>8.2319384334654</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.328455963161138</v>
+        <v>1.338010138767986</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.3832875871557915</v>
+        <v>0.8944186623581418</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8069</v>
+        <v>8114</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>571.4481822600269</v>
+        <v>694.2730555421067</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>149</v>
+        <v>180.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>49.27675662810946</v>
+        <v>45.96614923422477</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>25.47012019088522</v>
+        <v>22.90060215754997</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.336881986061324</v>
+        <v>2.245329928606275</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>1.322960083275782</v>
+        <v>1.153281946042281</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, cci_momentum</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, breakout_volume_confirm, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8050</v>
+        <v>8048</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>561.7690253847842</v>
+        <v>693.374159426352</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>60.7</v>
+        <v>52.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>53.48896840458392</v>
+        <v>61.26991338912921</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>26.70120716783505</v>
+        <v>13.21670549694385</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4501132058860908</v>
+        <v>1.328455963161138</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.0744357678458436</v>
+        <v>0.3832875869995589</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8182</v>
+        <v>8482</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>552.1782239085092</v>
+        <v>690.6104786768367</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>43.9</v>
+        <v>50.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>57.06543655433917</v>
+        <v>56.89196429307799</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>26.55620323367192</v>
+        <v>4.388619613716532</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.9282495929435975</v>
+        <v>0.167637607878647</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.4486938825086221</v>
+        <v>0.2218917532671633</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8091</v>
+        <v>8103</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>536.0835949382483</v>
+        <v>660.2479950323589</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>219.5</v>
+        <v>113.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>47.63225325914828</v>
+        <v>46.51966876202816</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>20.1848610444512</v>
+        <v>31.78935065786008</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.366746423426096</v>
+        <v>0.4249693177132852</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>1.487094445446179</v>
+        <v>-2.08272342851657</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8039</v>
+        <v>8111</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>533.1796036909162</v>
+        <v>657.3443960855127</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>296</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>54.59769323993281</v>
+        <v>56.4973543905852</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>20.80033066544986</v>
+        <v>39.46334219272779</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.8262922668966934</v>
+        <v>0.8790520595010514</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>1.901219661974297</v>
+        <v>0.7391356277250436</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8482</v>
+        <v>8240</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>530.6104786768367</v>
+        <v>648.8775930035322</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>50.5</v>
+        <v>54.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>56.89196429744831</v>
+        <v>55.20473592666379</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>4.388619635403045</v>
+        <v>36.60985093913929</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.167637607878647</v>
+        <v>0.196662363998827</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.2218917532431215</v>
+        <v>-0.2272161558634562</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8103</v>
+        <v>8059</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>530.2479950323587</v>
+        <v>598.4307810773935</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>113.5</v>
+        <v>18.75</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>46.51966882547542</v>
+        <v>66.12346788267854</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>31.78935062753724</v>
+        <v>28.12517838285132</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4249693177132852</v>
+        <v>1.39352187250845</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-2.082723429093252</v>
+        <v>0.150242790582825</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8110</v>
+        <v>8215</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>528.4193238761513</v>
+        <v>592.7527710957993</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>49.55</v>
+        <v>27.8</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>58.62306550732048</v>
+        <v>53.17571507626323</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>28.49003139434097</v>
+        <v>38.05655169985831</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4598969425881347</v>
+        <v>0.1942390485610783</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.1436949451467148</v>
+        <v>-0.1119964753843485</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8040</v>
+        <v>8038</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>526.5467139304491</v>
+        <v>576.103597864686</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>87.7</v>
+        <v>35.85</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>52.32616358679142</v>
+        <v>63.35929851337034</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>26.45482208759978</v>
+        <v>33.26524663590567</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.2557983348610487</v>
+        <v>0.7988541456623074</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.5845789536713228</v>
+        <v>0.3714072016032399</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8064</v>
+        <v>8476</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>526.3268883331768</v>
+        <v>566.3357893745675</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>128</v>
+        <v>21.4</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>49.599884427193</v>
+        <v>68.18608210006943</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>22.05331736799735</v>
+        <v>23.34116153936527</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.3582799019035891</v>
+        <v>1.367465055329062</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-1.500912700859437</v>
+        <v>0.2130077075310813</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8438</v>
+        <v>8050</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>523.919620719175</v>
+        <v>561.7690253847842</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>79.5</v>
+        <v>60.7</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>60.29668167005355</v>
+        <v>53.48896832736408</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>32.18921326093034</v>
+        <v>26.7012071359443</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6547582778465307</v>
+        <v>0.4501132058860908</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.4205746878466607</v>
+        <v>-0.0744357677497036</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8299</v>
+        <v>8182</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>502.2284394102805</v>
+        <v>552.1782239085092</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2055</v>
+        <v>43.9</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>47.28747558123427</v>
+        <v>57.06543653900853</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>11.96915149483924</v>
+        <v>26.55620321768136</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.615884953503735</v>
+        <v>0.9282495929435975</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-8.24504857502593</v>
+        <v>0.4486938825927505</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8147</v>
+        <v>8039</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>490.419557761142</v>
+        <v>543.1796036909162</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>141</v>
+        <v>296</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>54.10997857238342</v>
+        <v>54.59769318946408</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>30.89129825523157</v>
+        <v>20.80033057007995</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.8057613756236071</v>
+        <v>0.8262922668966934</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.3807223582730565</v>
+        <v>1.901219662719368</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8162</v>
+        <v>8940</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>490.171217547244</v>
+        <v>542.510660688746</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>65.5</v>
+        <v>15.25</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>55.43194342867664</v>
+        <v>56.92277653020634</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>24.24276566851924</v>
+        <v>12.83394902291484</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.9614484628596792</v>
+        <v>0.7985527894421116</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.2173579207459099</v>
+        <v>0.0549105617333083</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8081</v>
+        <v>8091</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>483.9572737650455</v>
+        <v>536.0835949382483</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>262.5</v>
+        <v>219.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>60.17824365532431</v>
+        <v>47.63225323941651</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>15.0613968007527</v>
+        <v>20.1848610444512</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.9863980664826718</v>
+        <v>1.366746423426096</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.548283644567257</v>
+        <v>1.487094445446179</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8043</v>
+        <v>8110</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>481.8655264314662</v>
+        <v>528.4193238761513</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>143.5</v>
+        <v>49.55</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>55.67965586587836</v>
+        <v>58.62306549290156</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16.20160649757927</v>
+        <v>28.4900314353536</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6816332662278141</v>
+        <v>0.4598969425881347</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.691873035418816</v>
+        <v>0.1436949451226792</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8227</v>
+        <v>8040</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>479.2274081042405</v>
+        <v>526.5467139304491</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>307.5</v>
+        <v>87.7</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>55.76278970006489</v>
+        <v>52.32616360674014</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45.75762868859045</v>
+        <v>26.45482213779751</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.285041395068367</v>
+        <v>0.2557983348610487</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>1</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-3.301214818997437</v>
+        <v>-0.5845789540078101</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8109</v>
+        <v>8064</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>468.567964413617</v>
+        <v>526.3268883331768</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>133.5</v>
+        <v>128</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>49.36403567583292</v>
+        <v>49.59988439188463</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>26.97745702031362</v>
+        <v>22.05331733652778</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6026853722854731</v>
+        <v>0.3582799019035891</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>1</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.0994403886003549</v>
+        <v>-1.50091270065513</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8038</v>
+        <v>9110</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>461.1035978646863</v>
+        <v>526.1227243449814</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>35.85</v>
+        <v>3.11</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>63.35929867401972</v>
+        <v>52.36184165001208</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>33.26524664527624</v>
+        <v>5.457239326864912</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.7988541456623074</v>
+        <v>2.212272434498137</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.3714072018195499</v>
+        <v>0.0730765410461444</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8074</v>
+        <v>8438</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>459.3818129998033</v>
+        <v>523.919620719175</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>55.5</v>
+        <v>79.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>55.19433909994053</v>
+        <v>60.29668164474015</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>23.48302810876578</v>
+        <v>32.18921325571947</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.7177397979640633</v>
+        <v>0.6547582778465307</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.75737083796905</v>
+        <v>0.4205746878466607</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8059</v>
+        <v>8112</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>458.4307810773935</v>
+        <v>511.3554475601783</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>18.75</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>66.12346784627601</v>
+        <v>51.45689469937242</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>28.12517836526904</v>
+        <v>18.00291731947333</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.39352187250845</v>
+        <v>1.111226569512267</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.1502427910565268</v>
+        <v>0.4801682958990365</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8072</v>
+        <v>8249</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>456.5345517204644</v>
+        <v>508.6053749844119</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>26.85</v>
+        <v>40.25</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>47.47315049370393</v>
+        <v>52.58676726462026</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>35.98651238210063</v>
+        <v>15.09522963715147</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3055345363273606</v>
+        <v>1.124364206656375</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.08607999701065611</v>
+        <v>0.2022434446920566</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8045</v>
+        <v>8104</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>455.4685422094315</v>
+        <v>504.8707987337952</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>55.5</v>
+        <v>31.15</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>55.77317244269106</v>
+        <v>50.81827384132336</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>23.58093945228387</v>
+        <v>16.05389931257042</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4702042765203744</v>
+        <v>0.9868329275149442</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.3684762923013673</v>
+        <v>0.0640933649907636</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8277</v>
+        <v>8299</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>444.8128817719419</v>
+        <v>502.2284394102805</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>15.35</v>
+        <v>2055</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>77.17323028554813</v>
+        <v>47.28747561788126</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>37.58997557537781</v>
+        <v>11.96915168190043</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.575258239335772</v>
+        <v>0.615884953503735</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0478250704607625</v>
+        <v>-8.245048578150454</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8467</v>
+        <v>8131</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>444.7843701569947</v>
+        <v>501.782832494465</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>92.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>55.63991064801917</v>
+        <v>66.35910789894821</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>8.231938495394811</v>
+        <v>18.17914576606385</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.338010138767986</v>
+        <v>2.047427689404284</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.8944186627186719</v>
+        <v>0.8713214000836859</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8383</v>
+        <v>8147</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>442.2748344725579</v>
+        <v>490.4195577611418</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>68.59999999999999</v>
+        <v>141</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>52.36053747930341</v>
+        <v>54.10997848477494</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>18.87611755930114</v>
+        <v>30.89129837866156</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.8513617780801241</v>
+        <v>0.8057613756236071</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.3482099681364453</v>
+        <v>-0.3807223586335611</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8926</v>
+        <v>8162</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>435.9026228630174</v>
+        <v>490.171217547244</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>59.8</v>
+        <v>65.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>54.18679438302562</v>
+        <v>55.43194343876024</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>15.22323557113792</v>
+        <v>24.24276580255305</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.407270234436472</v>
+        <v>0.9614484628596792</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.2421725712506018</v>
+        <v>0.2173579206858262</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8940</v>
+        <v>8043</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>427.5106606887466</v>
+        <v>481.8655264314662</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>15.25</v>
+        <v>143.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>56.92277645927306</v>
+        <v>55.67965585574525</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>12.83394882885043</v>
+        <v>16.20160658087314</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.7985527894421116</v>
+        <v>0.6816332662278141</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0549105617933947</v>
+        <v>1.69187303526258</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8466</v>
+        <v>8227</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>427.3485422775562</v>
+        <v>479.2274081042405</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>15.25</v>
+        <v>307.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>50.49866252575583</v>
+        <v>55.76278966654802</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>24.68607284596393</v>
+        <v>45.75762872498345</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.2561979409813509</v>
+        <v>1.285041395068367</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0637682586057627</v>
+        <v>-3.301214818516755</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8085</v>
+        <v>8109</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>403.2770427842439</v>
+        <v>468.5679644136172</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>14.6</v>
+        <v>133.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>53.17286769457368</v>
+        <v>49.36403572670845</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21.16495891469414</v>
+        <v>26.97745703788257</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.8838373160786424</v>
+        <v>0.6026853722854731</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.02096031841025</v>
+        <v>-0.0994403885042147</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8249</v>
+        <v>8074</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>398.605374984412</v>
+        <v>459.3818129998062</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>40.25</v>
+        <v>55.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>52.58676725379574</v>
+        <v>55.19433901754098</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>15.09522963715148</v>
+        <v>23.48302812707887</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.124364206656375</v>
+        <v>0.7177397979640633</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.2022434451967743</v>
+        <v>0.7573708374402903</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8476</v>
+        <v>8463</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>396.3357893745672</v>
+        <v>458.9885557314367</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>21.4</v>
+        <v>21.35</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>68.18608204862969</v>
+        <v>53.79845189671835</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>23.34116154726864</v>
+        <v>26.65527118060258</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.367465055329062</v>
+        <v>0.5697837768805321</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.2130077075190625</v>
+        <v>0.0189703335863514</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8104</v>
+        <v>8072</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>394.8707987337986</v>
+        <v>456.5345517204643</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>31.15</v>
+        <v>26.85</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>50.81827392621307</v>
+        <v>47.47315050455143</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>16.05389930891695</v>
+        <v>35.98651280810072</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.9868329275149442</v>
+        <v>0.3055345363273606</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0640933652070747</v>
+        <v>-0.0860799966381167</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>9110</v>
+        <v>8045</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>386.1227243449813</v>
+        <v>455.4685422094314</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>3.11</v>
+        <v>55.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>52.36184161124159</v>
+        <v>55.77317226728484</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>5.45723930728468</v>
+        <v>23.58093958948712</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2.212272434498137</v>
+        <v>0.4702042765203744</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.07307654112065171</v>
+        <v>0.3684762910996394</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8112</v>
+        <v>8277</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>381.3554475601784</v>
+        <v>444.8128817719419</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>85.59999999999999</v>
+        <v>15.35</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>51.45689473558621</v>
+        <v>77.17323034501121</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>18.00291731019679</v>
+        <v>37.58997567278981</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.111226569512267</v>
+        <v>0.575258239335772</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.4801682960192033</v>
+        <v>0.0478250704113323</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8131</v>
+        <v>8383</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>371.782832494465</v>
+        <v>442.2748344725579</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>66.35910789097346</v>
+        <v>52.36053747372031</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>18.17914567880097</v>
+        <v>18.87611763321262</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2.047427689404284</v>
+        <v>0.8513617780801241</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,48 +3750,48 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.8713214001798224</v>
+        <v>0.3482099678840817</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8183</v>
+        <v>8926</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>355.8634049635208</v>
+        <v>435.9026228630174</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>28.2</v>
+        <v>59.8</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G63" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>44.90268837163893</v>
+        <v>54.18679422407509</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>19.14537615931564</v>
+        <v>15.22323554824934</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.870816255095116</v>
+        <v>1.407270234436472</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0686206105644962</v>
+        <v>0.24217257146691</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8121</v>
+        <v>8466</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>353.1970581749778</v>
+        <v>427.3485422775562</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>33</v>
+        <v>15.25</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>58.93298994842496</v>
+        <v>50.49866253853401</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>34.26746896100257</v>
+        <v>24.68607280481957</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.9078593053007432</v>
+        <v>0.2561979409813509</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.5166043272379945</v>
+        <v>0.06376825855769321</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8463</v>
+        <v>9930</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>348.9885557314367</v>
+        <v>418.7901428823772</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>21.35</v>
+        <v>59</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>53.79845174116752</v>
+        <v>28.29251342930299</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>26.65527121664006</v>
+        <v>37.25903157350928</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.5697837768805321</v>
+        <v>1.128638130203463</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.01897033371854</v>
+        <v>-0.1282990097704694</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, cci_momentum, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8155</v>
+        <v>8085</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>348.4771663325829</v>
+        <v>403.2770427842439</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>319.5</v>
+        <v>14.6</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>45.69333793468663</v>
+        <v>53.17286752766778</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>11.46112960243353</v>
+        <v>21.16495891964747</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5040488961779231</v>
+        <v>0.8838373160786424</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.2586219638098628</v>
+        <v>-0.0209603183862149</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8488</v>
+        <v>8404</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>345.2633120529206</v>
+        <v>382.8916849861029</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>9.550000000000001</v>
+        <v>13.75</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>50.82284101363666</v>
+        <v>43.20795157066135</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>36.57997940475706</v>
+        <v>43.29873861882667</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5180327292176503</v>
+        <v>0.6119172428017007</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.3870628010124282</v>
+        <v>0.1307196246988241</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, williams_r_recovery, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8423</v>
+        <v>8080</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>330.7095077178674</v>
+        <v>362.7585735366969</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>17.85</v>
+        <v>28.05</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>46.7878816159797</v>
+        <v>51.39302708307459</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>21.44344658028098</v>
+        <v>30.47429952618275</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.6874469116476402</v>
+        <v>1.07182931023789</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0233510124795388</v>
+        <v>0.2530969791834686</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8464</v>
+        <v>9955</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>328.9250070260335</v>
+        <v>357.2311994306456</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>372.5</v>
+        <v>23.95</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>53.55228799045042</v>
+        <v>54.48491741884222</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>10.40551865460192</v>
+        <v>13.89196515363142</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.408649710434518</v>
+        <v>1.074449188511194</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,48 +4121,48 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1070166636413871</v>
+        <v>0.1475526061423308</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8054</v>
+        <v>8183</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>328.8154541684539</v>
+        <v>355.8634049635203</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>79.3</v>
+        <v>28.2</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G70" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>37.37295638064381</v>
+        <v>44.90268828233761</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>21.33625045814966</v>
+        <v>19.14537626240933</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.9641248402015968</v>
+        <v>1.870816255095116</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.6245879917019037</v>
+        <v>0.06862061036835659</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8071</v>
+        <v>8473</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>322.423880188952</v>
+        <v>354.5971084285252</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>21.65</v>
+        <v>39.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>41.69573964930489</v>
+        <v>42.73724799156396</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>9.779172071519854</v>
+        <v>20.35504353035504</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.4679561415265996</v>
+        <v>0.9104054611498028</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>3</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0618524408923907</v>
+        <v>0.2799588360049398</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8477</v>
+        <v>8121</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>320.649737704402</v>
+        <v>353.1970581749791</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>13.7</v>
+        <v>33</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>33.88278716115309</v>
+        <v>58.93298996182332</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>29.21299951149089</v>
+        <v>34.26746895320779</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.7630333550082083</v>
+        <v>0.9078593053007432</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.0660189527041555</v>
+        <v>0.5166043272019452</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8049</v>
+        <v>8155</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>317.6403178968899</v>
+        <v>348.4771663325829</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>24.5</v>
+        <v>319.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>45.72253508330767</v>
+        <v>45.69333791374839</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>13.97098266861219</v>
+        <v>11.46112960243353</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.1702597647519</v>
+        <v>0.5040488961779231</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>1</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.030997690422249</v>
+        <v>-0.2586219656123998</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8462</v>
+        <v>8488</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>315.7738494060165</v>
+        <v>345.2633120529206</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>155.5</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>36.36515699483189</v>
+        <v>50.82284102618739</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>33.74343380929167</v>
+        <v>36.57997949335141</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.349735587697994</v>
+        <v>0.5180327292176503</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.0783916936961115</v>
+        <v>-0.3870628010725144</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8096</v>
+        <v>8411</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>311.5627363023843</v>
+        <v>342.6646164433041</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>89.09999999999999</v>
+        <v>11.85</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>39.86579208020965</v>
+        <v>34.14488697607236</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>30.35653271343551</v>
+        <v>37.77459773142525</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.867266526738583</v>
+        <v>0.6741668742567738</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>1.474364632517918</v>
+        <v>-0.0336005630759287</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8440</v>
+        <v>8423</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>310.8198712941126</v>
+        <v>330.7095077178674</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>20.15</v>
+        <v>17.85</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>49.6299842158875</v>
+        <v>46.78788155908508</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>18.82743087847691</v>
+        <v>21.44344659715605</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.115390653431999</v>
+        <v>0.6874469116476402</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0082002378937042</v>
+        <v>-0.0233510124675211</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8087</v>
+        <v>8054</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>303.3562894537462</v>
+        <v>328.8154541684539</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>23</v>
+        <v>79.3</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>48.54991246316855</v>
+        <v>37.37295630662079</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>4.97081263096085</v>
+        <v>21.33625047396295</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.7804514510927982</v>
+        <v>0.9641248402015968</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0374935031104394</v>
+        <v>-0.6245879917019037</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8410</v>
+        <v>8071</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>302.5571111798168</v>
+        <v>322.4238801889518</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>26.4</v>
+        <v>21.65</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>19.70438406094108</v>
+        <v>41.69573938114745</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>50.2544745439509</v>
+        <v>9.77917204320018</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.2822624768946395</v>
+        <v>0.4679561415265996</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.1258800221916782</v>
+        <v>0.0618524410245791</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8047</v>
+        <v>8477</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>301.3994250669911</v>
+        <v>320.649737704402</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>45.05</v>
+        <v>13.7</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>50.54409140706516</v>
+        <v>33.88278704310588</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>8.495280986088185</v>
+        <v>29.21299951065169</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.3746830819474883</v>
+        <v>0.7630333550082083</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.4288579148386691</v>
+        <v>-0.066018952632052</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8261</v>
+        <v>8049</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>300.3052141194533</v>
+        <v>317.6403178968899</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>176.5</v>
+        <v>24.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>46.34385209873371</v>
+        <v>45.72253491519356</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>16.46505829783872</v>
+        <v>13.97098268947804</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.5748772264009738</v>
+        <v>1.1702597647519</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>1.233198753448287</v>
+        <v>0.0309976904462858</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8097</v>
+        <v>8462</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>297.5281733608412</v>
+        <v>315.7738494060165</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>48.2</v>
+        <v>155.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>38.68162119062995</v>
+        <v>36.36515680193286</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>17.05842488545245</v>
+        <v>33.743433871365</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.5075764419329044</v>
+        <v>1.349735587697994</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0517035565193</v>
+        <v>-0.0783916933356008</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8443</v>
+        <v>8096</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>295.8836632395605</v>
+        <v>311.5627363023843</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>0</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>1.950460958477308</v>
+        <v>39.86579209917904</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>55.69526877967227</v>
+        <v>30.35653273219902</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.0224086756524085</v>
+        <v>0.867266526738583</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.7061348557798258</v>
+        <v>1.474364632301604</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8271</v>
+        <v>8440</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>293.7178727358681</v>
+        <v>310.8198712941121</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>197</v>
+        <v>20.15</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>36.66385584598137</v>
+        <v>49.62998436680947</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>13.82388325272908</v>
+        <v>18.82743092843217</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.163529192093045</v>
+        <v>1.115390653431999</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.191978300287948</v>
+        <v>-0.008200238061947401</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8499</v>
+        <v>8210</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>293.2654643067827</v>
+        <v>308.0870030076985</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>251.5</v>
+        <v>861</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>50.35670287940766</v>
+        <v>39.92407159106165</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>8.3630609319207</v>
+        <v>18.51694185643326</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.9911493473803812</v>
+        <v>1.038216707725866</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>1.951983249721599</v>
+        <v>4.903996857471341</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8102</v>
+        <v>8087</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>283.2727080690869</v>
+        <v>303.3562894537462</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>59.8</v>
+        <v>23</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>50.83276723484622</v>
+        <v>48.5499124376772</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>4.949070449099335</v>
+        <v>4.970812654848594</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.9772751905776942</v>
+        <v>0.7804514510927982</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>1.302667246983498</v>
+        <v>0.0374935031104394</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -4979,21 +4979,21 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8176</v>
+        <v>8410</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>259.6795214836725</v>
+        <v>302.5571111798168</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>9.74</v>
+        <v>26.4</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>45.52536632268671</v>
+        <v>19.70438388930785</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>24.99832995555923</v>
+        <v>50.25447450025505</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.8502382970909512</v>
+        <v>0.2822624768946395</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.0038130629641106</v>
+        <v>-0.1258800221195748</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8291</v>
+        <v>8047</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>256.0765902410481</v>
+        <v>301.3994250669915</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>27.1</v>
+        <v>45.05</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>35.71618001525688</v>
+        <v>50.5440914103817</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>5.52796952044739</v>
+        <v>8.495280948590747</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.9527412989442596</v>
+        <v>0.3746830819474883</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0274602812433411</v>
+        <v>0.4288579148867386</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>9912</v>
+        <v>8261</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>250.0950177761388</v>
+        <v>300.3052141194535</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>0</v>
+        <v>176.5</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>6.159002773273741</v>
+        <v>46.34385209319696</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>37.5183331690496</v>
+        <v>16.46505826896959</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.022983980801616</v>
+        <v>0.5748772264009738</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.8350163729258107</v>
+        <v>1.233198753207958</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8374</v>
+        <v>8097</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>249.4295292863081</v>
+        <v>297.5281733608412</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>48.2</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>38.84879570320389</v>
+        <v>38.68162043109961</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>11.40301389659556</v>
+        <v>17.05842505398328</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.817635814882572</v>
+        <v>0.5075764419329044</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0921620371498432</v>
+        <v>0.0517035569759553</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8473</v>
+        <v>8443</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>244.5971084285249</v>
+        <v>295.8836632395605</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>39.5</v>
+        <v>0</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>42.73724805373021</v>
+        <v>1.950460958477308</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>20.35504352812701</v>
+        <v>55.69526883123445</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.9104054611498028</v>
+        <v>0.0224086756524085</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.2799588360770433</v>
+        <v>-0.7061348557678097</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8404</v>
+        <v>8499</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>242.8916849861029</v>
+        <v>293.2654643067827</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>13.75</v>
+        <v>251.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>43.20795146536886</v>
+        <v>50.35670268145363</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>43.29873853911605</v>
+        <v>8.363061107698002</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6119172428017007</v>
+        <v>0.9911493473803812</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.1307196247709272</v>
+        <v>1.951983254047801</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>9930</v>
+        <v>8102</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>233.7901428823772</v>
+        <v>283.2727080690869</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>59</v>
+        <v>59.8</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>28.29251342930299</v>
+        <v>50.83276721226267</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>37.25903154519936</v>
+        <v>4.949070576680589</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.128638130203463</v>
+        <v>0.9772751905776942</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.1282990097464429</v>
+        <v>1.302667247247881</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8411</v>
+        <v>8271</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>227.664616443304</v>
+        <v>278.7178727358681</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>11.85</v>
+        <v>197</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>34.14488680366894</v>
+        <v>36.66385582956951</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>37.77459778214296</v>
+        <v>13.8238833173438</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.6741668742567738</v>
+        <v>1.163529192093045</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.0336005630278596</v>
+        <v>0.191978300287948</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8101</v>
+        <v>8176</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>221.7974834880878</v>
+        <v>259.6795214836725</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>10.35</v>
+        <v>9.74</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>42.78485675942599</v>
+        <v>45.52536733837333</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>17.57149876221875</v>
+        <v>24.99832990225935</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.2797300471719076</v>
+        <v>0.8502382970909512</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.109262143685803</v>
+        <v>-0.0038130632044565</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8044</v>
+        <v>8291</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>217.3780324848701</v>
+        <v>256.0765902410479</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>24.1</v>
+        <v>27.1</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>48.77235383627338</v>
+        <v>35.71636714277848</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>17.78867355044731</v>
+        <v>5.527759353854743</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5875484271851138</v>
+        <v>0.9527412989442596</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.1044936825522092</v>
+        <v>0.0274548200585396</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>9955</v>
+        <v>9912</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>217.2311994306457</v>
+        <v>250.0950177761388</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>23.95</v>
+        <v>0</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>54.48491752948004</v>
+        <v>6.15900276644625</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>13.89196512962126</v>
+        <v>37.51833329168685</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.074449188511194</v>
+        <v>0.022983980801616</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.1475526061182959</v>
+        <v>-0.8350163729137938</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8454</v>
+        <v>8374</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>216.9753546967578</v>
+        <v>249.4295292863083</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>243</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>49.37024161120082</v>
+        <v>38.84879575047196</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>11.73378165054335</v>
+        <v>11.403013894549</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4431635260944335</v>
+        <v>0.817635814882572</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.7922573070116599</v>
+        <v>-0.0921620384717611</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8472</v>
+        <v>8105</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>216.0471700843833</v>
+        <v>225.7966468487758</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>64.40000000000001</v>
+        <v>14.95</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>34.29358418804611</v>
+        <v>45.89122277570002</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>28.65358770180813</v>
+        <v>18.92248779658171</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.5047170084383219</v>
+        <v>0.6189868271455392</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-1.202951951369743</v>
+        <v>0.0585356304766954</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8088</v>
+        <v>8390</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>196.3125113514096</v>
+        <v>225.0358556891336</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>44</v>
+        <v>92.7</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>50.92235835163282</v>
+        <v>50.07488039024588</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>13.93218736276069</v>
+        <v>18.92684252562286</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.6434064823022029</v>
+        <v>1.424378627186152</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>1</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.3406921216247782</v>
+        <v>0.4281046489452844</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8210</v>
+        <v>8101</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>193.0870030076985</v>
+        <v>221.7974834880877</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>861</v>
+        <v>10.35</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>39.92407156748629</v>
+        <v>42.7848567042487</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>18.51694191054202</v>
+        <v>17.57149870010306</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.038216707725866</v>
+        <v>0.2797300471719076</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>4.903996861557097</v>
+        <v>-0.1092621436136989</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8222</v>
+        <v>8044</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>190.9716493565871</v>
+        <v>217.3780324848701</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>35.05</v>
+        <v>24.1</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>40.29447018574571</v>
+        <v>48.77235376413265</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>8.487428533146289</v>
+        <v>17.7886735504473</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.4222937875437331</v>
+        <v>0.5875484271851138</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0973255835690602</v>
+        <v>0.1044936825642266</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8076</v>
+        <v>8454</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>186.2963105351124</v>
+        <v>216.9753546967578</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>21.2</v>
+        <v>243</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>37.96048060933946</v>
+        <v>49.37024161959241</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>21.99181417252735</v>
+        <v>11.73378163346272</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.249588760848608</v>
+        <v>0.4431635260944335</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0371388439422307</v>
+        <v>0.7922573068914684</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>9136</v>
+        <v>8472</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>185.556143426974</v>
+        <v>216.0471700843833</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>9.109999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>30.77259510721088</v>
+        <v>34.29358394417257</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>15.8544799378246</v>
+        <v>28.65358769711379</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5261595654136273</v>
+        <v>0.5047170084383219</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0570599268216096</v>
+        <v>-1.202951950528529</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8163</v>
+        <v>8088</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>183.2225320998292</v>
+        <v>196.3125113514096</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>29.75</v>
+        <v>44</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>41.96910086865044</v>
+        <v>50.92235842611424</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>12.48436782103308</v>
+        <v>13.93218746582667</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.8281193430550805</v>
+        <v>0.6434064823022029</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0400344470186307</v>
+        <v>0.3406921214685574</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8422</v>
+        <v>8222</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>183.1093511879026</v>
+        <v>190.971649356587</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>25.4</v>
+        <v>35.05</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>42.00479105134401</v>
+        <v>40.29447023068475</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>8.015757526405702</v>
+        <v>8.487428547550287</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.9550871723325084</v>
+        <v>0.4222937875437331</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0096409460930679</v>
+        <v>0.09732558292012899</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8080</v>
+        <v>8076</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>162.7585735366969</v>
+        <v>186.296310535113</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>28.05</v>
+        <v>21.2</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>51.39302652473098</v>
+        <v>37.96048068052349</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>30.47429952505365</v>
+        <v>21.99181419152471</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.07182931023789</v>
+        <v>1.249588760848608</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.2530969791834686</v>
+        <v>0.0371388438460902</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8481</v>
+        <v>9136</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>158.1433833466204</v>
+        <v>185.5561434269739</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>40.3</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>39.37249315749514</v>
+        <v>30.77259512691863</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>12.02079692081729</v>
+        <v>15.85447997160353</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.146632095768743</v>
+        <v>0.5261595654136273</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0603113351752968</v>
+        <v>0.0570599267951719</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8487</v>
+        <v>8163</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>150.4727603910946</v>
+        <v>183.2225320998293</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>70.09999999999999</v>
+        <v>29.75</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>42.90424351613235</v>
+        <v>41.96910077762077</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>11.63291951518418</v>
+        <v>12.48436782103308</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.8542160102147236</v>
+        <v>0.8281193430550805</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0221843967004639</v>
+        <v>0.0400344469705622</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8341</v>
+        <v>8422</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>126.9993229868972</v>
+        <v>183.1093511879026</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>74</v>
+        <v>25.4</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>40.83845258283507</v>
+        <v>42.00478930153159</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>12.65397637931326</v>
+        <v>8.0157575264057</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.7857869823293556</v>
+        <v>0.9550871723325084</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0046371238887085</v>
+        <v>-0.009640945475200601</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8429</v>
+        <v>8478</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>117.9047660513767</v>
+        <v>181.5425034802055</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>5.89</v>
+        <v>139.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>41.92243341086926</v>
+        <v>42.64927649608858</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>7.706639828761142</v>
+        <v>7.712550538418987</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.6192782245866622</v>
+        <v>0.7576257302110431</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.005581591514106</v>
+        <v>0.11062600299149</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8105</v>
+        <v>8481</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>115.7966468487758</v>
+        <v>178.1433833466204</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>14.95</v>
+        <v>40.3</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>45.89122278823594</v>
+        <v>39.37249315749514</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>18.92248781331815</v>
+        <v>12.02079692081729</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6189868271455392</v>
+        <v>1.146632095768743</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0585356305339052</v>
+        <v>-0.0603113351752968</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8390</v>
+        <v>8487</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>110.0358556891338</v>
+        <v>170.4727603910946</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>92.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>50.07488042495618</v>
+        <v>42.90424355459746</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>18.92684252238376</v>
+        <v>11.63291955281123</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.424378627186152</v>
+        <v>0.8542160102147236</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.4281046487770452</v>
+        <v>0.0221843967004639</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8067</v>
+        <v>8341</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>88.45479775711055</v>
+        <v>126.9993229868972</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>11.1</v>
+        <v>74</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>40.23668234145907</v>
+        <v>40.83845254107062</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>17.47286112530384</v>
+        <v>12.65397642934859</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.2438307009029677</v>
+        <v>0.7857869823293556</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0467991303934097</v>
+        <v>-0.0046371240088665</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8478</v>
+        <v>8429</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>71.54250348020535</v>
+        <v>117.9047660513767</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>139.5</v>
+        <v>5.89</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.64927603138448</v>
+        <v>41.92243361179273</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>7.712550517389018</v>
+        <v>7.706639825319261</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.7576257302110431</v>
+        <v>0.6192782245866622</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,9 +6506,62 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.110626004433558</v>
+        <v>0.0055815914996842</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>8067</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>志旭</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>88.45479775711057</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>40.23667903930817</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>17.47286128701573</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.2438307009029677</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-0.0467991272448774</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
